--- a/deliverables/RACI - pulse!.xlsx
+++ b/deliverables/RACI - pulse!.xlsx
@@ -17,12 +17,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="46">
   <si>
     <t>RACI - pulse!</t>
   </si>
   <si>
-    <t>Версия 0.2. Роли трех участников распределены предварительно по просьбе инициатора; команда может изменить назначение.</t>
+    <t>Версия 0.2. Строки связаны с планом по кодам WBS.</t>
   </si>
   <si>
     <t>WBS</t>
@@ -31,10 +31,10 @@
     <t>Пакет / решение</t>
   </si>
   <si>
-    <t>Team Lead / аналитик</t>
-  </si>
-  <si>
-    <t>Данные и ML</t>
+    <t>Заказчик / руководитель</t>
+  </si>
+  <si>
+    <t>Данные и модели</t>
   </si>
   <si>
     <t>Разработка</t>
@@ -43,7 +43,7 @@
     <t>Тесты и документы</t>
   </si>
   <si>
-    <t>Учебный заказчик</t>
+    <t>Преподаватель</t>
   </si>
   <si>
     <t>Игроки пилота</t>
@@ -133,10 +133,16 @@
     <t>Документы и передача</t>
   </si>
   <si>
-    <t>6.2-6.3</t>
-  </si>
-  <si>
-    <t>Приемка результата</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Исправления и приемка заказчиком</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>Передача и проверка на курсе</t>
   </si>
   <si>
     <t>Правило</t>
@@ -925,31 +931,57 @@
       <c r="B16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>18</v>
+      <c r="C16" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>14</v>
+      <c r="E16" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="31" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -960,10 +992,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>

--- a/deliverables/RACI - pulse!.xlsx
+++ b/deliverables/RACI - pulse!.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="RACI" sheetId="1" r:id="rId1"/>
+    <sheet name="Роли" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RACI!$A$1:$H$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RACI!$A$1:$H$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="65">
   <si>
     <t>RACI - pulse!</t>
   </si>
@@ -31,130 +32,187 @@
     <t>Пакет / решение</t>
   </si>
   <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>ПРЕП</t>
+  </si>
+  <si>
+    <t>ИГР</t>
+  </si>
+  <si>
+    <t>1.1-1.3</t>
+  </si>
+  <si>
+    <t>Паспорт, границы и ТЗ</t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Схема сырых попыток</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Проверка импорта API и карт</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Договориться о передаче попыток</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Собрать попытки добровольцев</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>Очистить и проверить данные</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Скиллсеты и признаки</t>
+  </si>
+  <si>
+    <t>3.2-3.3</t>
+  </si>
+  <si>
+    <t>Профиль и сложность карты</t>
+  </si>
+  <si>
+    <t>3.4-3.5</t>
+  </si>
+  <si>
+    <t>Модели pass и accuracy</t>
+  </si>
+  <si>
+    <t>4.1-4.2</t>
+  </si>
+  <si>
+    <t>Интерфейс и интеграция</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Автоматические тесты</t>
+  </si>
+  <si>
+    <t>5.2-5.3</t>
+  </si>
+  <si>
+    <t>Пилот и оценка качества</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>Документы и передача</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Исправления и приемка заказчиком</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>Передача и проверка на курсе</t>
+  </si>
+  <si>
+    <t>Правило</t>
+  </si>
+  <si>
+    <t>На каждой строке ровно один A и минимум один R. A/R означает, что один участник отвечает и выполняет.</t>
+  </si>
+  <si>
+    <t>Обозначения</t>
+  </si>
+  <si>
+    <t>R - делает; A - отвечает за итог; C - консультирует до решения; I - получает информацию после решения.</t>
+  </si>
+  <si>
+    <t>Столбец</t>
+  </si>
+  <si>
+    <t>Роль</t>
+  </si>
+  <si>
+    <t>Участник</t>
+  </si>
+  <si>
     <t>Заказчик / руководитель</t>
   </si>
   <si>
+    <t>Ляхов Я.П.</t>
+  </si>
+  <si>
     <t>Данные и модели</t>
   </si>
   <si>
+    <t>Недугов Д.</t>
+  </si>
+  <si>
     <t>Разработка</t>
   </si>
   <si>
+    <t>Гайфуллин А.Р.</t>
+  </si>
+  <si>
     <t>Тесты и документы</t>
   </si>
   <si>
-    <t>Преподаватель</t>
+    <t>Темиров А.М.</t>
+  </si>
+  <si>
+    <t>Проверяет проект по требованиям курса</t>
+  </si>
+  <si>
+    <t>Преподаватель курса</t>
+  </si>
+  <si>
+    <t>Пробуют приложение и дают обратную связь</t>
   </si>
   <si>
     <t>Игроки пилота</t>
-  </si>
-  <si>
-    <t>1.1-1.3</t>
-  </si>
-  <si>
-    <t>Паспорт, границы и ТЗ</t>
-  </si>
-  <si>
-    <t>A/R</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>Схема сырых попыток</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>2.2</t>
-  </si>
-  <si>
-    <t>Проверка импорта API и карт</t>
-  </si>
-  <si>
-    <t>2.3-2.5</t>
-  </si>
-  <si>
-    <t>Сбор пилотных данных</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>Скиллсеты и признаки</t>
-  </si>
-  <si>
-    <t>3.2-3.3</t>
-  </si>
-  <si>
-    <t>Профиль и сложность карты</t>
-  </si>
-  <si>
-    <t>3.4-3.5</t>
-  </si>
-  <si>
-    <t>Модели pass и accuracy</t>
-  </si>
-  <si>
-    <t>4.1-4.2</t>
-  </si>
-  <si>
-    <t>Интерфейс и интеграция</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>Автоматические тесты</t>
-  </si>
-  <si>
-    <t>5.2-5.3</t>
-  </si>
-  <si>
-    <t>Пилот и оценка качества</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>Документы и передача</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>Исправления и приемка заказчиком</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>Передача и проверка на курсе</t>
-  </si>
-  <si>
-    <t>Правило</t>
-  </si>
-  <si>
-    <t>На каждой строке ровно один A и минимум один R. A/R означает, что один участник отвечает и выполняет.</t>
-  </si>
-  <si>
-    <t>Обозначения</t>
-  </si>
-  <si>
-    <t>R - делает; A - отвечает за итог; C - консультирует до решения; I - получает информацию после решения.</t>
   </si>
 </sst>
 </file>
@@ -580,12 +638,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="8" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="42.7109375" customWidth="1"/>
+    <col min="3" max="8" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -724,16 +782,16 @@
         <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>18</v>
+      <c r="F8" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>14</v>
@@ -752,14 +810,14 @@
       <c r="C9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>14</v>
@@ -781,17 +839,17 @@
       <c r="D10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>18</v>
+      <c r="E10" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31" customHeight="1">
@@ -807,8 +865,8 @@
       <c r="D11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>18</v>
+      <c r="E11" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>13</v>
@@ -816,8 +874,8 @@
       <c r="G11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>19</v>
+      <c r="H11" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31" customHeight="1">
@@ -830,11 +888,11 @@
       <c r="C12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>13</v>
@@ -856,17 +914,17 @@
       <c r="C13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>18</v>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>12</v>
+      <c r="F13" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>19</v>
@@ -882,17 +940,17 @@
       <c r="C14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="D14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="F14" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="G14" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>13</v>
@@ -905,20 +963,20 @@
       <c r="B15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G15" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>19</v>
@@ -931,23 +989,23 @@
       <c r="B16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>14</v>
+      <c r="H16" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="31" customHeight="1">
@@ -957,61 +1015,209 @@
       <c r="B17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="31" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="31" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="H19" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B23:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="48.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="35" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="35" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="35" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="35" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="35" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="35" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
 </file>